--- a/tests/vlaanderen/reference/tussenresultaten/groepenverdeling/2023/Verdeling_over_groepen_Beroepsbevolking_alleen_autobezit.xlsx
+++ b/tests/vlaanderen/reference/tussenresultaten/groepenverdeling/2023/Verdeling_over_groepen_Beroepsbevolking_alleen_autobezit.xlsx
@@ -727,16 +727,16 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>0.007508982035928145</v>
+        <v>0.007508982035928144</v>
       </c>
       <c r="E2">
         <v>0.1213952095808383</v>
       </c>
       <c r="F2">
-        <v>0.04855808383233533</v>
+        <v>0.04855808383233532</v>
       </c>
       <c r="G2">
-        <v>0.06069760479041917</v>
+        <v>0.06069760479041916</v>
       </c>
       <c r="H2">
         <v>0.01213952095808383</v>
@@ -766,25 +766,25 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.004855808383233534</v>
+        <v>0.004855808383233532</v>
       </c>
       <c r="R2">
         <v>0.0001501796407185629</v>
       </c>
       <c r="S2">
-        <v>0.007358802395209582</v>
+        <v>0.007358802395209581</v>
       </c>
       <c r="T2">
-        <v>0.1189673053892216</v>
+        <v>0.1189673053892215</v>
       </c>
       <c r="U2">
-        <v>0.04758692215568863</v>
+        <v>0.04758692215568862</v>
       </c>
       <c r="V2">
-        <v>0.05948365269461079</v>
+        <v>0.05948365269461077</v>
       </c>
       <c r="W2">
-        <v>0.01189673053892216</v>
+        <v>0.01189673053892215</v>
       </c>
       <c r="X2">
         <v>0</v>
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.04248832335329341</v>
+        <v>0.0424883233532934</v>
       </c>
       <c r="AG2">
         <v>0.001314071856287425</v>
@@ -865,7 +865,7 @@
         <v>0.005417964071856287</v>
       </c>
       <c r="AX2">
-        <v>0.08759041916167663</v>
+        <v>0.08759041916167665</v>
       </c>
       <c r="AY2">
         <v>0.03503616766467066</v>
@@ -951,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.004859877800407332</v>
+        <v>0.004859877800407331</v>
       </c>
       <c r="R3">
-        <v>0.0001503054989816701</v>
+        <v>0.00015030549898167</v>
       </c>
       <c r="S3">
         <v>0.007364969450101832</v>
@@ -963,7 +963,7 @@
         <v>0.1190670061099796</v>
       </c>
       <c r="U3">
-        <v>0.04762680244399186</v>
+        <v>0.04762680244399185</v>
       </c>
       <c r="V3">
         <v>0.05953350305498981</v>
@@ -1005,13 +1005,13 @@
         <v>0.006174898167006109</v>
       </c>
       <c r="AI3">
-        <v>0.09982752036659878</v>
+        <v>0.09982752036659877</v>
       </c>
       <c r="AJ3">
         <v>0.03993100814663951</v>
       </c>
       <c r="AK3">
-        <v>0.04991376018329939</v>
+        <v>0.04991376018329938</v>
       </c>
       <c r="AL3">
         <v>0.009982752036659878</v>
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="AU3">
-        <v>0.06682331975560084</v>
+        <v>0.06682331975560082</v>
       </c>
       <c r="AV3">
-        <v>0.002066700610997964</v>
+        <v>0.002066700610997963</v>
       </c>
       <c r="AW3">
-        <v>0.00544857433808554</v>
+        <v>0.005448574338085539</v>
       </c>
       <c r="AX3">
-        <v>0.08808528513238287</v>
+        <v>0.08808528513238285</v>
       </c>
       <c r="AY3">
         <v>0.03523411405295315</v>
@@ -1059,7 +1059,7 @@
         <v>0.04404264256619143</v>
       </c>
       <c r="BA3">
-        <v>0.008808528513238288</v>
+        <v>0.008808528513238286</v>
       </c>
       <c r="BB3">
         <v>0</v>
@@ -1097,19 +1097,19 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0.007484210526315791</v>
+        <v>0.007484210526315789</v>
       </c>
       <c r="E4">
         <v>0.1209947368421053</v>
       </c>
       <c r="F4">
-        <v>0.04839789473684211</v>
+        <v>0.0483978947368421</v>
       </c>
       <c r="G4">
-        <v>0.06049736842105265</v>
+        <v>0.06049736842105263</v>
       </c>
       <c r="H4">
-        <v>0.01209947368421053</v>
+        <v>0.01209947368421052</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1136,25 +1136,25 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0.004860210526315788</v>
+        <v>0.004860210526315789</v>
       </c>
       <c r="R4">
         <v>0.0001503157894736842</v>
       </c>
       <c r="S4">
-        <v>0.007365473684210526</v>
+        <v>0.007365473684210527</v>
       </c>
       <c r="T4">
-        <v>0.1190751578947368</v>
+        <v>0.1190751578947369</v>
       </c>
       <c r="U4">
-        <v>0.04763006315789474</v>
+        <v>0.04763006315789475</v>
       </c>
       <c r="V4">
-        <v>0.05953757894736842</v>
+        <v>0.05953757894736843</v>
       </c>
       <c r="W4">
-        <v>0.01190751578947368</v>
+        <v>0.01190751578947369</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -1235,13 +1235,13 @@
         <v>0.005448947368421053</v>
       </c>
       <c r="AX4">
-        <v>0.0880913157894737</v>
+        <v>0.08809131578947368</v>
       </c>
       <c r="AY4">
         <v>0.03523652631578947</v>
       </c>
       <c r="AZ4">
-        <v>0.04404565789473685</v>
+        <v>0.04404565789473684</v>
       </c>
       <c r="BA4">
         <v>0.008809131578947367</v>
@@ -1321,10 +1321,10 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0.004865015479876162</v>
+        <v>0.004865015479876161</v>
       </c>
       <c r="R5">
-        <v>0.0001504643962848298</v>
+        <v>0.0001504643962848297</v>
       </c>
       <c r="S5">
         <v>0.007372755417956656</v>
@@ -1339,7 +1339,7 @@
         <v>0.03575786377708978</v>
       </c>
       <c r="W5">
-        <v>0.0119192879256966</v>
+        <v>0.01191928792569659</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -1372,19 +1372,19 @@
         <v>0.00130843653250774</v>
       </c>
       <c r="AH5">
-        <v>0.006168343653250775</v>
+        <v>0.006168343653250774</v>
       </c>
       <c r="AI5">
-        <v>0.1396101780185759</v>
+        <v>0.1396101780185758</v>
       </c>
       <c r="AJ5">
-        <v>0.01994431114551084</v>
+        <v>0.01994431114551083</v>
       </c>
       <c r="AK5">
         <v>0.02991646671826625</v>
       </c>
       <c r="AL5">
-        <v>0.009972155572755419</v>
+        <v>0.009972155572755416</v>
       </c>
       <c r="AM5">
         <v>0</v>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.004858493870402803</v>
+        <v>0.004858493870402802</v>
       </c>
       <c r="R6">
         <v>0.0001502626970227671</v>
       </c>
       <c r="S6">
-        <v>0.007362872154115587</v>
+        <v>0.007362872154115586</v>
       </c>
       <c r="T6">
         <v>0.1666463397548161</v>
@@ -1563,7 +1563,7 @@
         <v>0.1402890105078809</v>
       </c>
       <c r="AJ6">
-        <v>0.02004128721541156</v>
+        <v>0.02004128721541155</v>
       </c>
       <c r="AK6">
         <v>0.03006193082311734</v>
@@ -1602,7 +1602,7 @@
         <v>0.002051663747810858</v>
       </c>
       <c r="AW6">
-        <v>0.005408931698774079</v>
+        <v>0.00540893169877408</v>
       </c>
       <c r="AX6">
         <v>0.1224221541155867</v>
@@ -1697,7 +1697,7 @@
         <v>0.00015</v>
       </c>
       <c r="S7">
-        <v>0.007349999999999998</v>
+        <v>0.00735</v>
       </c>
       <c r="T7">
         <v>0.2020025</v>
@@ -1706,7 +1706,7 @@
         <v>0.0118825</v>
       </c>
       <c r="V7">
-        <v>0.02376499999999999</v>
+        <v>0.023765</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -1742,7 +1742,7 @@
         <v>0.0013125</v>
       </c>
       <c r="AH7">
-        <v>0.006187500000000001</v>
+        <v>0.0061875</v>
       </c>
       <c r="AI7">
         <v>0.170053125</v>
@@ -1837,16 +1837,16 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.007497722441542668</v>
+        <v>0.007497722441542667</v>
       </c>
       <c r="E8">
-        <v>0.06060658973580323</v>
+        <v>0.06060658973580321</v>
       </c>
       <c r="F8">
-        <v>0.06060658973580323</v>
+        <v>0.06060658973580321</v>
       </c>
       <c r="G8">
-        <v>0.07272790768296387</v>
+        <v>0.07272790768296386</v>
       </c>
       <c r="H8">
         <v>0.04848527178864259</v>
@@ -1882,7 +1882,7 @@
         <v>0.00015013665350744</v>
       </c>
       <c r="S8">
-        <v>0.007356696021864559</v>
+        <v>0.00735669602186456</v>
       </c>
       <c r="T8">
         <v>0.05946662617673854</v>
@@ -1927,7 +1927,7 @@
         <v>0.001312101427269966</v>
       </c>
       <c r="AH8">
-        <v>0.0061856210142727</v>
+        <v>0.006185621014272701</v>
       </c>
       <c r="AI8">
         <v>0.05000043653203766</v>
@@ -1972,16 +1972,16 @@
         <v>0.002061873671424234</v>
       </c>
       <c r="AW8">
-        <v>0.005435848770118433</v>
+        <v>0.005435848770118434</v>
       </c>
       <c r="AX8">
-        <v>0.04393977755845733</v>
+        <v>0.04393977755845734</v>
       </c>
       <c r="AY8">
-        <v>0.04393977755845733</v>
+        <v>0.04393977755845734</v>
       </c>
       <c r="AZ8">
-        <v>0.0527277330701488</v>
+        <v>0.05272773307014881</v>
       </c>
       <c r="BA8">
         <v>0.03515182204676587</v>
@@ -2028,7 +2028,7 @@
         <v>0.120956416464891</v>
       </c>
       <c r="F9">
-        <v>0.04838256658595641</v>
+        <v>0.04838256658595642</v>
       </c>
       <c r="G9">
         <v>0.06047820823244551</v>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0.004861743341404359</v>
+        <v>0.004861743341404358</v>
       </c>
       <c r="R9">
         <v>0.000150363196125908</v>
@@ -2112,7 +2112,7 @@
         <v>0.001309322033898305</v>
       </c>
       <c r="AH9">
-        <v>0.006172518159806296</v>
+        <v>0.006172518159806295</v>
       </c>
       <c r="AI9">
         <v>0.09978904358353512</v>
@@ -2157,16 +2157,16 @@
         <v>0.002067493946731235</v>
       </c>
       <c r="AW9">
-        <v>0.005450665859564164</v>
+        <v>0.005450665859564165</v>
       </c>
       <c r="AX9">
-        <v>0.08811909806295398</v>
+        <v>0.088119098062954</v>
       </c>
       <c r="AY9">
         <v>0.03524763922518159</v>
       </c>
       <c r="AZ9">
-        <v>0.04405954903147699</v>
+        <v>0.044059549031477</v>
       </c>
       <c r="BA9">
         <v>0.008811909806295398</v>
@@ -2246,13 +2246,13 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0.004821965317919074</v>
+        <v>0.004821965317919075</v>
       </c>
       <c r="R10">
         <v>0.0001491329479768786</v>
       </c>
       <c r="S10">
-        <v>0.00730751445086705</v>
+        <v>0.007307514450867051</v>
       </c>
       <c r="T10">
         <v>0.2008348554913295</v>
@@ -2261,7 +2261,7 @@
         <v>0.01181381502890173</v>
       </c>
       <c r="V10">
-        <v>0.02362763005780346</v>
+        <v>0.02362763005780347</v>
       </c>
       <c r="W10">
         <v>0</v>
@@ -2336,19 +2336,19 @@
         <v>0</v>
       </c>
       <c r="AU10">
-        <v>0.06630202312138728</v>
+        <v>0.06630202312138726</v>
       </c>
       <c r="AV10">
         <v>0.002050578034682081</v>
       </c>
       <c r="AW10">
-        <v>0.00540606936416185</v>
+        <v>0.005406069364161849</v>
       </c>
       <c r="AX10">
         <v>0.1485768063583815</v>
       </c>
       <c r="AY10">
-        <v>0.008739812138728325</v>
+        <v>0.008739812138728324</v>
       </c>
       <c r="AZ10">
         <v>0.01747962427745665</v>
@@ -2392,13 +2392,13 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.007741935483870968</v>
+        <v>0.007741935483870967</v>
       </c>
       <c r="E11">
         <v>0.2127741935483871</v>
       </c>
       <c r="F11">
-        <v>0.01251612903225807</v>
+        <v>0.01251612903225806</v>
       </c>
       <c r="G11">
         <v>0.02503225806451613</v>
@@ -2431,19 +2431,19 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0.004693548387096774</v>
+        <v>0.004693548387096775</v>
       </c>
       <c r="R11">
         <v>0.0001451612903225806</v>
       </c>
       <c r="S11">
-        <v>0.00711290322580645</v>
+        <v>0.007112903225806451</v>
       </c>
       <c r="T11">
         <v>0.1954862903225807</v>
       </c>
       <c r="U11">
-        <v>0.01149919354838709</v>
+        <v>0.0114991935483871</v>
       </c>
       <c r="V11">
         <v>0.02299838709677419</v>
@@ -2479,10 +2479,10 @@
         <v>0.04106854838709677</v>
       </c>
       <c r="AG11">
-        <v>0.00127016129032258</v>
+        <v>0.001270161290322581</v>
       </c>
       <c r="AH11">
-        <v>0.005987903225806451</v>
+        <v>0.005987903225806452</v>
       </c>
       <c r="AI11">
         <v>0.1645675403225806</v>
@@ -2521,19 +2521,19 @@
         <v>0</v>
       </c>
       <c r="AU11">
-        <v>0.06883870967741937</v>
+        <v>0.06883870967741934</v>
       </c>
       <c r="AV11">
-        <v>0.002129032258064517</v>
+        <v>0.002129032258064516</v>
       </c>
       <c r="AW11">
-        <v>0.005612903225806452</v>
+        <v>0.005612903225806451</v>
       </c>
       <c r="AX11">
-        <v>0.1542612903225807</v>
+        <v>0.1542612903225806</v>
       </c>
       <c r="AY11">
-        <v>0.009074193548387097</v>
+        <v>0.009074193548387096</v>
       </c>
       <c r="AZ11">
         <v>0.01814838709677419</v>
@@ -2661,13 +2661,13 @@
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.0429746835443038</v>
+        <v>0.04297468354430379</v>
       </c>
       <c r="AG12">
         <v>0.001329113924050633</v>
       </c>
       <c r="AH12">
-        <v>0.006265822784810127</v>
+        <v>0.006265822784810126</v>
       </c>
       <c r="AI12">
         <v>0.1722056962025316</v>
@@ -2706,19 +2706,19 @@
         <v>0</v>
       </c>
       <c r="AU12">
-        <v>0.06584335443037975</v>
+        <v>0.06584335443037974</v>
       </c>
       <c r="AV12">
         <v>0.002036392405063291</v>
       </c>
       <c r="AW12">
-        <v>0.00536867088607595</v>
+        <v>0.005368670886075949</v>
       </c>
       <c r="AX12">
-        <v>0.1475489715189874</v>
+        <v>0.1475489715189873</v>
       </c>
       <c r="AY12">
-        <v>0.008679351265822786</v>
+        <v>0.008679351265822784</v>
       </c>
       <c r="AZ12">
         <v>0.01735870253164557</v>
@@ -2765,7 +2765,7 @@
         <v>0.007538461538461538</v>
       </c>
       <c r="E13">
-        <v>0.2071820512820512</v>
+        <v>0.2071820512820513</v>
       </c>
       <c r="F13">
         <v>0.01218717948717949</v>
@@ -2801,22 +2801,22 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0.004775384615384615</v>
+        <v>0.004775384615384616</v>
       </c>
       <c r="R13">
         <v>0.0001476923076923077</v>
       </c>
       <c r="S13">
-        <v>0.007236923076923076</v>
+        <v>0.007236923076923077</v>
       </c>
       <c r="T13">
-        <v>0.1988947692307692</v>
+        <v>0.1988947692307693</v>
       </c>
       <c r="U13">
         <v>0.01169969230769231</v>
       </c>
       <c r="V13">
-        <v>0.02339938461538461</v>
+        <v>0.02339938461538462</v>
       </c>
       <c r="W13">
         <v>0</v>
@@ -2846,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.04265512820512821</v>
+        <v>0.0426551282051282</v>
       </c>
       <c r="AG13">
         <v>0.001319230769230769</v>
@@ -2861,7 +2861,7 @@
         <v>0.01005442307692308</v>
       </c>
       <c r="AK13">
-        <v>0.02010884615384616</v>
+        <v>0.02010884615384615</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2897,16 +2897,16 @@
         <v>0.002073076923076923</v>
       </c>
       <c r="AW13">
-        <v>0.005465384615384615</v>
+        <v>0.005465384615384614</v>
       </c>
       <c r="AX13">
         <v>0.1502069871794872</v>
       </c>
       <c r="AY13">
-        <v>0.008835705128205128</v>
+        <v>0.008835705128205126</v>
       </c>
       <c r="AZ13">
-        <v>0.01767141025641026</v>
+        <v>0.01767141025641025</v>
       </c>
       <c r="BA13">
         <v>0</v>
